--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:19</t>
+    <t xml:space="preserve">2026-09-09 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:14</t>
+    <t xml:space="preserve">2026-09-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:10</t>
+    <t xml:space="preserve">2026-09-23 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:39</t>
+    <t xml:space="preserve">2026-10-02 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Bárbara</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:36</t>
+    <t xml:space="preserve">2026-10-04 09:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:07</t>
+    <t xml:space="preserve">2026-10-05 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
